--- a/tests/fixtures/lom/33612-1-LOM.xlsx
+++ b/tests/fixtures/lom/33612-1-LOM.xlsx
@@ -51,29 +51,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>SPUD, VALVE SUPPORT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33638-1</t>
+          <t>28275-3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TOE KICK, SIDE</t>
         </is>
       </c>
     </row>
@@ -85,81 +85,455 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28273-2</t>
+          <t>33638-1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>PIPE CAP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28275-1</t>
+          <t>33611-1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>CORNER VERT. RAIL, STRAIGHT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>56657</t>
+          <t>28287-1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIRST RELEASE</t>
+          <t>GATE REST</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>28278-1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PLATFORM GATE WELDMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28282-1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LANYARD ANCHOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>28273-2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CAP PLATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>28281-1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>STIFFENER</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>28266-1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VERT. RAIL, STRAIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>28274-2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HORIZ. INTERMED. RAIL, FRONT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>33613-1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HORIZ. INTERMED. RAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>28265-2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HORIZ. INTERMED. RAIL, LOWER GATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>28265-1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HORIZ. INTERMED. RAIL, SIDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>28268-1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FLOOR SUPPORT, OUTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>28269-1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FLOOR SUPPORT, INNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>28270-1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MOUNTING TUBE WELDMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>28283-1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PLATFORM DECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>28276-1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TOE KICK, FRONT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>28275-2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TOE KICK, SIDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>28275-1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TOE KICK, REAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>56657</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FIRST RELEASE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>BT</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>97879</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>PROPERTY OF TIME</t>
         </is>
@@ -212,29 +586,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>SPUD, VALVE SUPPORT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33638-1</t>
+          <t>28275-3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TOE KICK, SIDE</t>
         </is>
       </c>
     </row>
@@ -246,39 +620,413 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28273-2</t>
+          <t>33638-1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>PIPE CAP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>33611-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CORNER VERT. RAIL, STRAIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>28287-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GATE REST</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>28278-1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PLATFORM GATE WELDMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28282-1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LANYARD ANCHOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>28273-2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CAP PLATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>28281-1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>STIFFENER</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>28266-1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VERT. RAIL, STRAIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>28274-2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HORIZ. INTERMED. RAIL, FRONT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>33613-1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HORIZ. INTERMED. RAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>28265-2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HORIZ. INTERMED. RAIL, LOWER GATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>28265-1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HORIZ. INTERMED. RAIL, SIDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>28268-1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FLOOR SUPPORT, OUTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>28269-1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FLOOR SUPPORT, INNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>28270-1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MOUNTING TUBE WELDMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>28283-1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PLATFORM DECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>28276-1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TOE KICK, FRONT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>28275-2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TOE KICK, SIDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>28275-1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TUBE</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TOE KICK, REAR</t>
         </is>
       </c>
     </row>
